--- a/Progress/coding/Global_tracker.XLSX
+++ b/Progress/coding/Global_tracker.XLSX
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I503"/>
+  <dimension ref="A1:I595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9003,6 +9003,2606 @@
         <is>
           <t>29Jun2026</t>
         </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>221 - Maximal Square</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Array / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>1</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>15jul2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>440 - K-th Smallest in Lexicographical Order</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Trie</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>29jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>1569 - Number of Ways to Reorder Array to Get Same BST</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Array / Math</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>1</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>21jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>761 - Special Binary String</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>String / Divide and Conquer</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>1</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>10jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>1348 - Tweet Counts Per Frequency</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Hash Table / String</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>1</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>08jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>493 - Reverse Pairs</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Array / Binary Search</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>1</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>08jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>363 - Max Sum of Rectangle No Larger Than K</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Array / Binary Search</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>1</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>07jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>403 - Frog Jump</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Array / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>1</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>06jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>330 - Patching Array</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Array / Greedy</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>1</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>04jun2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>1411 - Number of Ways to Paint N × 3 Grid</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>1</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>23may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2040 - Kth Smallest Product of Two Sorted Arrays</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Array / Binary Search</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>1</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>22may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>815 - Bus Routes</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>1</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>22may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2791 - Count Paths That Can Form a Palindrome in a Tree</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Hash Table / Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>1</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>22may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>1373 - Maximum Sum BST in Binary Tree</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Dynamic Programming / Tree</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>1</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>21may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2179 - Count Good Triplets in an Array</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Array / Binary Search</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>1</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>21may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>1534 - Count Good Triplets</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Array / Enumeration</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>1</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>21may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>158 - Read N Characters Given read4 II - Call Multiple Times</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Array / Simulation</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>1</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>17may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>3735 - Lexicographically Smallest String After Reverse II</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>String / Binary Search</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>1</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>17may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2223 - Sum of Scores of Built Strings</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>String / Binary Search</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>1</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>14may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>3076 - Shortest Uncommon Substring in an Array</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>1</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>14may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>10 - Regular Expression Matching</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>String / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>1</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>01may2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>759 - Employee Free Time</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Array / Sweep Line</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>1</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>26apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2523 - Closest Prime Numbers in Range</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Math / Number Theory</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>1</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>16apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>904 - Fruit Into Baskets</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>1</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>16apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>638 - Shopping Offers</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Array / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>1</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>16apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>755 - Pour Water</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Array / Simulation</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>1</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>16apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>400 - Nth Digit</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Math / Binary Search</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>1</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>16apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>622 - Design Circular Queue</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Array / Linked List</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>1</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>16apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>1257 - Smallest Common Region</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>1</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>07apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>1058 - Minimize Rounding Error to Meet Target</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Array / Math</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>1</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>07apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>983 - Minimum Cost For Tickets</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Array / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>1</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>06apr2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>864 - Shortest Path to Get All Keys</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Array / Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>1</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>27mar2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>3484 - Design Spreadsheet</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>1</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>27mar2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2571 - Minimum Operations to Reduce an Integer to 0</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Dynamic Programming / Greedy</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>1</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>22feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>425 - Word Squares</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Array / String</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>1</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>20feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>428 - Serialize and Deserialize N-ary Tree</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>String / Tree</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>1</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>20feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2209 - Minimum White Tiles After Covering With Carpets</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>String / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>1</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>18feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>1896 - Minimum Cost to Change the Final Value of Expression</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Math / String</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>1</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>18feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>411 - Minimum Unique Word Abbreviation</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Array / String</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>1</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>17feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>1147 - Longest Chunked Palindrome Decomposition</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Two Pointers / String</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>1</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>11feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>1096 - Brace Expansion II</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Hash Table / String</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>1</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>10feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>527 - Word Abbreviation</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Array / String</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>1</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>09feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>471 - Encode String with Shortest Length</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>String / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>1</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>09feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2851 - String Transformation</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Math / String</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>1</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>08feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>1106 - Parsing A Boolean Expression</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>String / Stack</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>1</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>03feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>854 - K-Similar Strings</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Hash Table / String</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>1</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>03feb2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>839 - Similar String Groups</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>1</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>23jan2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>1987 - Number of Unique Good Subsequences</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>String / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>1</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>16jan2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>1406 - Stone Game III</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Array / Math</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>1</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>31dec2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>772 - Basic Calculator III</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Math / String</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>1</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>24dec2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>44 - Wildcard Matching</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>String / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>1</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>11nov2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>741 - Cherry Pickup</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Array / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>1</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>08nov2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2577 - Minimum Time to Visit a Cell In a Grid</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Array / Breadth-First Search</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>1</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>06nov2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2933 - High-Access Employees</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>1</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>28oct2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>1366 - Rank Teams by Votes</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>1</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>28oct2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>751 - IP to CIDR</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>String / Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>1</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>28oct2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>353 - Design Snake Game</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>1</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>27oct2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>621 - Task Scheduler</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>1</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>26jul2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>402 - Remove K Digits</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>String / Stack</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>1</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>26jul2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2566 - Maximum Difference by Remapping a Digit</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Math / Greedy</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>1</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>26jul2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>29 - Divide Two Integers</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Math / Bit Manipulation</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>1</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>04jul2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>443 - String Compression</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Two Pointers / String</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>1</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>26jun2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>341 - Flatten Nested List Iterator</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Stack / Tree</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>1</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>24jun2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>1400 - Construct K Palindrome Strings</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Hash Table / String</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>1</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>14jun2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2751 - Robot Collisions</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Array / Stack</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>1</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>12jun2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>846 - Hand of Straights</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>1</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>10may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>229 - Majority Element II</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>1</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>10may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>95 - Unique Binary Search Trees II</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Dynamic Programming / Backtracking</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>1</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>10may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>96 - Unique Binary Search Trees</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Math / Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>1</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>10may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>1899 - Merge Triplets to Form Target Triplet</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Array / Greedy</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>1</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>06may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>36 - Valid Sudoku</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>1</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>06may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>40 - Combination Sum II</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Array / Backtracking</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>1</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>05may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>1448 - Count Good Nodes in Binary Tree</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Tree / Depth-First Search</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>1</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>05may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>3043 - Find the Length of the Longest Common Prefix</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Array / Hash Table</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>1</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>05may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2579 - Count Total Number of Colored Cells</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>1</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>05may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>567 - Permutation in String</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Hash Table / Two Pointers</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>1</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>04may2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>1044 - Longest Duplicate Substring</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>1392 - Longest Happy Prefix</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>214 - Shortest Palindrome</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>1140 - Stone Game II</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>877 - Stone Game</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>843 - Guess the Word</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>337 - House Robber III</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>664 - Strange Printer</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>502 - IPO</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>857 - Minimum Cost to Hire K Workers</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>871 - Minimum Number of Refueling Stops</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>135 - Candy</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>372 - Super Pow</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>204 - Count Primes</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>1568 - Minimum Number of Days to Disconnect Island</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>834 - Sum of Distances in Tree</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Progress/coding/Global_tracker.XLSX
+++ b/Progress/coding/Global_tracker.XLSX
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I595"/>
+  <dimension ref="A1:I596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4505,6 +4505,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Array / Sorting / Prefix Sum</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5117,6 +5122,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Array / Two Pointers / Sorting / Heap</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11301,6 +11311,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>String / Binary Search / Rolling Hash</t>
+        </is>
+      </c>
       <c r="E580" t="n">
         <v>1</v>
       </c>
@@ -11321,6 +11336,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>String / KMP / Z-algorithm</t>
+        </is>
+      </c>
       <c r="E581" t="n">
         <v>1</v>
       </c>
@@ -11341,6 +11361,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>String / KMP / Rolling Hash</t>
+        </is>
+      </c>
       <c r="E582" t="n">
         <v>1</v>
       </c>
@@ -11361,6 +11386,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Math / Game Theory / DP</t>
+        </is>
+      </c>
       <c r="E583" t="n">
         <v>1</v>
       </c>
@@ -11381,6 +11411,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Math / Game Theory / DP</t>
+        </is>
+      </c>
       <c r="E584" t="n">
         <v>1</v>
       </c>
@@ -11401,6 +11436,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Array / String / Interactive</t>
+        </is>
+      </c>
       <c r="E585" t="n">
         <v>1</v>
       </c>
@@ -11421,6 +11461,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Tree / DFS / DP</t>
+        </is>
+      </c>
       <c r="E586" t="n">
         <v>1</v>
       </c>
@@ -11441,6 +11486,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>String / DP / Interval DP</t>
+        </is>
+      </c>
       <c r="E587" t="n">
         <v>1</v>
       </c>
@@ -11461,6 +11511,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Array / Greedy / Heap</t>
+        </is>
+      </c>
       <c r="E588" t="n">
         <v>1</v>
       </c>
@@ -11481,6 +11536,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Array / Greedy / Heap / Sorting</t>
+        </is>
+      </c>
       <c r="E589" t="n">
         <v>1</v>
       </c>
@@ -11501,6 +11561,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Array / Greedy / Heap</t>
+        </is>
+      </c>
       <c r="E590" t="n">
         <v>1</v>
       </c>
@@ -11521,6 +11586,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Array / Greedy</t>
+        </is>
+      </c>
       <c r="E591" t="n">
         <v>1</v>
       </c>
@@ -11541,6 +11611,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Math / Divide and Conquer</t>
+        </is>
+      </c>
       <c r="E592" t="n">
         <v>1</v>
       </c>
@@ -11561,6 +11636,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Array / Math / Number Theory</t>
+        </is>
+      </c>
       <c r="E593" t="n">
         <v>1</v>
       </c>
@@ -11581,6 +11661,11 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Array / DFS / BFS / Articulation Point</t>
+        </is>
+      </c>
       <c r="E594" t="n">
         <v>1</v>
       </c>
@@ -11601,8 +11686,43 @@
           <t>Hard</t>
         </is>
       </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Tree / DFS / Graph / Rerooting</t>
+        </is>
+      </c>
       <c r="E595" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>902 - Numbers At Most N Given Digit Set</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>digit dp</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>1</v>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>16jul2026</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Progress/coding/Global_tracker.XLSX
+++ b/Progress/coding/Global_tracker.XLSX
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I600"/>
+  <dimension ref="A1:I604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.862142857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -15192,6 +15192,138 @@
       <c r="G600" s="6" t="n"/>
       <c r="H600" s="6" t="n"/>
       <c r="I600" s="6" t="n"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B601" s="6" t="inlineStr">
+        <is>
+          <t>1359 - Count All Valid Pickup and Delivery Options</t>
+        </is>
+      </c>
+      <c r="C601" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D601" s="6" t="inlineStr">
+        <is>
+          <t>Math / Combinatorics / AP Series</t>
+        </is>
+      </c>
+      <c r="E601" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F601" s="6" t="inlineStr">
+        <is>
+          <t>08aug2026</t>
+        </is>
+      </c>
+      <c r="G601" s="6" t="n"/>
+      <c r="H601" s="6" t="n"/>
+      <c r="I601" s="6" t="n"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B602" s="6" t="inlineStr">
+        <is>
+          <t>187 - Repeated DNA Sequences</t>
+        </is>
+      </c>
+      <c r="C602" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D602" s="6" t="inlineStr">
+        <is>
+          <t>String / Rolling Hash / Rabin-Karp</t>
+        </is>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F602" s="6" t="inlineStr">
+        <is>
+          <t>15aug2026</t>
+        </is>
+      </c>
+      <c r="G602" s="6" t="n"/>
+      <c r="H602" s="6" t="n"/>
+      <c r="I602" s="6" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B603" s="6" t="inlineStr">
+        <is>
+          <t>936 - Stamping the Sequence</t>
+        </is>
+      </c>
+      <c r="C603" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D603" s="6" t="inlineStr">
+        <is>
+          <t>String / Greedy / Reverse Simulation</t>
+        </is>
+      </c>
+      <c r="E603" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F603" s="6" t="inlineStr">
+        <is>
+          <t>15aug2026</t>
+        </is>
+      </c>
+      <c r="G603" s="6" t="n"/>
+      <c r="H603" s="6" t="n"/>
+      <c r="I603" s="6" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B604" s="6" t="inlineStr">
+        <is>
+          <t>2472 - Maximum Number of Non-Overlapping Palindrome Substrings</t>
+        </is>
+      </c>
+      <c r="C604" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D604" s="6" t="inlineStr">
+        <is>
+          <t>String / Palindrome DP / Interval DP</t>
+        </is>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F604" s="6" t="inlineStr">
+        <is>
+          <t>20aug2026</t>
+        </is>
+      </c>
+      <c r="G604" s="6" t="n"/>
+      <c r="H604" s="6" t="n"/>
+      <c r="I604" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Progress/coding/Global_tracker.XLSX
+++ b/Progress/coding/Global_tracker.XLSX
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I604"/>
+  <dimension ref="A1:I606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.862142857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -15324,6 +15324,72 @@
       <c r="G604" s="6" t="n"/>
       <c r="H604" s="6" t="n"/>
       <c r="I604" s="6" t="n"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B605" s="6" t="inlineStr">
+        <is>
+          <t>1510 - Stone Game IV</t>
+        </is>
+      </c>
+      <c r="C605" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D605" s="6" t="inlineStr">
+        <is>
+          <t>Game Theory / Sprague-Grundy / DP</t>
+        </is>
+      </c>
+      <c r="E605" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F605" s="6" t="inlineStr">
+        <is>
+          <t>22aug2026</t>
+        </is>
+      </c>
+      <c r="G605" s="6" t="n"/>
+      <c r="H605" s="6" t="n"/>
+      <c r="I605" s="6" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B606" s="6" t="inlineStr">
+        <is>
+          <t>464 - Can I Win</t>
+        </is>
+      </c>
+      <c r="C606" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D606" s="6" t="inlineStr">
+        <is>
+          <t>Game Theory / Bitmask DP / Memoized Search</t>
+        </is>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F606" s="6" t="inlineStr">
+        <is>
+          <t>22aug2026</t>
+        </is>
+      </c>
+      <c r="G606" s="6" t="n"/>
+      <c r="H606" s="6" t="n"/>
+      <c r="I606" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
